--- a/estadistica2/data/herrera_navarro.xlsx
+++ b/estadistica2/data/herrera_navarro.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kennethbunker/Library/CloudStorage/Dropbox/GitHub/uss/estadistica2/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E7399F7-E335-404B-BE19-5BABAC4071DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7A61625-18D6-4946-8872-7958F17752C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
     <sheet name="codebook" sheetId="2" r:id="rId2"/>
+    <sheet name="variables" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">codebook!$A$1:$E$1</definedName>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1915" uniqueCount="331">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1926" uniqueCount="339">
   <si>
     <t>id</t>
   </si>
@@ -1030,6 +1031,30 @@
   <si>
     <t>max</t>
   </si>
+  <si>
+    <t>categorica</t>
+  </si>
+  <si>
+    <t>VD</t>
+  </si>
+  <si>
+    <t>VI1</t>
+  </si>
+  <si>
+    <t>VI2</t>
+  </si>
+  <si>
+    <t>VI3</t>
+  </si>
+  <si>
+    <t>VI4</t>
+  </si>
+  <si>
+    <t>CONTINUA</t>
+  </si>
+  <si>
+    <t>DUMMY</t>
+  </si>
 </sst>
 </file>
 
@@ -1109,7 +1134,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1126,14 +1151,11 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -16560,7 +16582,7 @@
         <v>144</v>
       </c>
       <c r="J194" s="1">
-        <f t="shared" ref="J194:J257" si="3">I194-H194</f>
+        <f t="shared" ref="J194:J233" si="3">I194-H194</f>
         <v>1092</v>
       </c>
       <c r="K194" s="6">
@@ -19696,6 +19718,9 @@
       <c r="A3" s="8" t="s">
         <v>1</v>
       </c>
+      <c r="C3" t="s">
+        <v>331</v>
+      </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="8" t="s">
@@ -19708,77 +19733,77 @@
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A6" s="10" t="s">
+      <c r="A6" s="8" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A7" s="10" t="s">
+      <c r="A7" s="8" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A8" s="10" t="s">
+      <c r="A8" s="8" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A9" s="10" t="s">
+      <c r="A9" s="8" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A10" s="10" t="s">
+      <c r="A10" s="8" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A11" s="10" t="s">
+      <c r="A11" s="8" t="s">
         <v>320</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A12" s="10" t="s">
+      <c r="A12" s="8" t="s">
         <v>322</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A13" s="11" t="s">
+      <c r="A13" s="10" t="s">
         <v>323</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A14" s="11" t="s">
+      <c r="A14" s="10" t="s">
         <v>321</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A15" s="11" t="s">
+      <c r="A15" s="10" t="s">
         <v>324</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A16" s="10" t="s">
+      <c r="A16" s="8" t="s">
         <v>325</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A17" s="10" t="s">
+      <c r="A17" s="8" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A18" s="10" t="s">
+      <c r="A18" s="8" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A19" s="10" t="s">
+      <c r="A19" s="8" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A20" s="10" t="s">
+      <c r="A20" s="8" t="s">
         <v>12</v>
       </c>
     </row>
@@ -68897,4 +68922,54 @@
   <autoFilter ref="A1:E1" xr:uid="{3570097C-913A-444F-969E-92A4586973FF}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C985BED-BEAF-DC47-9CBA-88067910A5DF}">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>332</v>
+      </c>
+      <c r="C1" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>333</v>
+      </c>
+      <c r="C2" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>334</v>
+      </c>
+      <c r="C3" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>335</v>
+      </c>
+      <c r="C4" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>336</v>
+      </c>
+      <c r="C5" t="s">
+        <v>338</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/estadistica2/data/herrera_navarro.xlsx
+++ b/estadistica2/data/herrera_navarro.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kennethbunker/Library/CloudStorage/Dropbox/GitHub/uss/estadistica2/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{417D4955-F4D5-2248-8081-95698A20073D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1888EA34-EDD9-AE42-8839-86B9C8874CA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1672" uniqueCount="339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1672" uniqueCount="340">
   <si>
     <t>name</t>
   </si>
@@ -1054,6 +1054,9 @@
   </si>
   <si>
     <t>sexo (dummy)</t>
+  </si>
+  <si>
+    <t>debut</t>
   </si>
 </sst>
 </file>
@@ -1623,7 +1626,7 @@
         <v>311</v>
       </c>
       <c r="J1" s="21" t="s">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="K1" s="3" t="s">
         <v>312</v>

--- a/estadistica2/data/herrera_navarro.xlsx
+++ b/estadistica2/data/herrera_navarro.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kennethbunker/Library/CloudStorage/Dropbox/GitHub/uss/estadistica2/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1888EA34-EDD9-AE42-8839-86B9C8874CA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D120DE29-D31E-444B-B575-E965D9231E9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1592,7 +1592,7 @@
     <col min="7" max="7" width="16.5" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9.1640625" style="5" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="8.83203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="19" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.83203125" style="2" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.1640625" style="2"/>
     <col min="12" max="12" width="19.5" style="2" customWidth="1"/>
   </cols>
